--- a/Documentos/Diccionario de datos.xlsx
+++ b/Documentos/Diccionario de datos.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="172">
   <si>
     <t>Diccionario de datos de Card Details DB</t>
   </si>
@@ -73,13 +73,13 @@
     <t>Rareza</t>
   </si>
   <si>
-    <t>Nivel de rareza de la carta.</t>
+    <t>Nivel de rareza de la carta.(Comun, Poco comun, Rara, Epica, Legendaria)</t>
   </si>
   <si>
     <t>Enum</t>
   </si>
   <si>
-    <t>Valor entre 1 y 5</t>
+    <t>No puede estar vacío</t>
   </si>
   <si>
     <t>EsInicial</t>
@@ -130,7 +130,10 @@
     <t>Objetivo</t>
   </si>
   <si>
-    <t xml:space="preserve">Carta a la que va dirigido el efecto </t>
+    <t>Carta a la que va dirigido el efecto  (aliado, personaje, enemigo,etc)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No puede estar vacío </t>
   </si>
   <si>
     <t>Duracion</t>
@@ -151,10 +154,7 @@
     <t>Trigger</t>
   </si>
   <si>
-    <t>Condición que activa el efecto.</t>
-  </si>
-  <si>
-    <t>No puede estar vacío (inicio, fin, flechas, al atacar)</t>
+    <t>Condición que activa el efecto.(inicio, fin, flechas, al atacar)</t>
   </si>
   <si>
     <t>Flechas</t>
@@ -163,9 +163,6 @@
     <t>Dirección a la que se propaga el efecto.</t>
   </si>
   <si>
-    <t>Debe ser uno de los valores predefinidos (los lados de un hexágono)</t>
-  </si>
-  <si>
     <t>Efecto</t>
   </si>
   <si>
@@ -495,15 +492,12 @@
     <t>Resultado</t>
   </si>
   <si>
-    <t xml:space="preserve">Resultado de la partida </t>
+    <t>Resultado de la partida (ganó, perdió, empate)</t>
   </si>
   <si>
     <t>ENUM</t>
   </si>
   <si>
-    <t>Valor predefinido (ganó, perdió, empate)</t>
-  </si>
-  <si>
     <t>Partida</t>
   </si>
   <si>
@@ -551,10 +545,7 @@
     <t>Modo</t>
   </si>
   <si>
-    <t>Modo de juego en el que se va a jugar</t>
-  </si>
-  <si>
-    <t>Debe ser un valor predefinido (modo vs, carrera, etc)</t>
+    <t>Modo de juego en el que se va a jugar (modo vs, carrera, etc)</t>
   </si>
   <si>
     <t>Sesión</t>
@@ -1189,14 +1180,16 @@
       <c r="C18" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="4"/>
+      <c r="D18" s="4" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>31</v>
@@ -1207,30 +1200,30 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22">
@@ -1244,12 +1237,12 @@
         <v>16</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25">
@@ -1271,13 +1264,13 @@
         <v>27</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27">
@@ -1285,13 +1278,13 @@
         <v>3</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28">
@@ -1299,7 +1292,7 @@
         <v>10</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>12</v>
@@ -1310,21 +1303,21 @@
     </row>
     <row r="29">
       <c r="A29" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B29" s="4" t="s">
         <v>52</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>53</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32">
@@ -1343,24 +1336,24 @@
     </row>
     <row r="33">
       <c r="A33" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B33" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>57</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B34" s="4" t="s">
         <v>59</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>60</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>31</v>
@@ -1371,10 +1364,10 @@
     </row>
     <row r="35">
       <c r="A35" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" s="4" t="s">
         <v>61</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>62</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>31</v>
@@ -1391,7 +1384,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="38">
@@ -1410,24 +1403,24 @@
     </row>
     <row r="39">
       <c r="A39" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B39" s="4" t="s">
         <v>64</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>65</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B40" s="4" t="s">
         <v>67</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>68</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>31</v>
@@ -1438,7 +1431,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="43">
@@ -1457,24 +1450,24 @@
     </row>
     <row r="44">
       <c r="A44" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>31</v>
@@ -1485,7 +1478,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="48">
@@ -1504,24 +1497,24 @@
     </row>
     <row r="49">
       <c r="A49" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B50" s="4" t="s">
         <v>76</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>77</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>31</v>
@@ -1532,7 +1525,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="53">
@@ -1551,47 +1544,47 @@
     </row>
     <row r="54">
       <c r="A54" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B54" s="4" t="s">
         <v>79</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>80</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B55" s="4" t="s">
         <v>82</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>83</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>26</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D56" s="6"/>
     </row>
     <row r="58">
       <c r="G58" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -1618,12 +1611,12 @@
   <sheetData>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6">
@@ -1642,69 +1635,69 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>90</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>91</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="C8" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="4" t="s">
         <v>95</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>98</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>100</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>101</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="C11" s="4" t="s">
         <v>104</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>105</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>21</v>
@@ -1712,13 +1705,13 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="C12" s="4" t="s">
         <v>107</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>108</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>21</v>
@@ -1726,38 +1719,38 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>110</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="C14" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>112</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>114</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>115</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>31</v>
@@ -1768,7 +1761,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19">
@@ -1787,10 +1780,10 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>24</v>
@@ -1799,22 +1792,22 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>119</v>
-      </c>
       <c r="C21" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D21" s="6"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>120</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>121</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>31</v>
@@ -1825,16 +1818,16 @@
     </row>
     <row r="23">
       <c r="A23" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="C23" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>124</v>
-      </c>
       <c r="D23" s="4" t="s">
-        <v>125</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24">
@@ -1844,7 +1837,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="26">
@@ -1863,38 +1856,38 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>31</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>31</v>
@@ -1905,13 +1898,13 @@
     </row>
     <row r="30">
       <c r="A30" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>21</v>
@@ -1919,21 +1912,21 @@
     </row>
     <row r="31">
       <c r="A31" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="34">
@@ -1952,24 +1945,24 @@
     </row>
     <row r="35">
       <c r="A35" s="4" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>24</v>
@@ -1978,10 +1971,10 @@
     </row>
     <row r="37">
       <c r="A37" s="4" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>12</v>
@@ -1992,10 +1985,10 @@
     </row>
     <row r="38">
       <c r="A38" s="4" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>12</v>
@@ -2006,13 +1999,13 @@
     </row>
     <row r="39">
       <c r="A39" s="4" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>21</v>
@@ -2020,7 +2013,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="42">
@@ -2039,24 +2032,24 @@
     </row>
     <row r="43">
       <c r="A43" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>152</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>24</v>
@@ -2065,22 +2058,22 @@
     </row>
     <row r="45">
       <c r="A45" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B45" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B45" s="4" t="s">
-        <v>91</v>
-      </c>
       <c r="C45" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D45" s="4"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>12</v>
@@ -2091,30 +2084,30 @@
     </row>
     <row r="47">
       <c r="A47" s="4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="49">
@@ -2152,40 +2145,40 @@
         <v>8</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="57">
@@ -2207,7 +2200,7 @@
         <v>6</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>24</v>
@@ -2216,10 +2209,10 @@
     </row>
     <row r="59">
       <c r="A59" s="4" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>24</v>
